--- a/mission/Template_dico_données+(3).xlsx
+++ b/mission/Template_dico_données+(3).xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Desktop\Openclassrooms2026\P5_Manipulez_une_base_de_données_avec_SQL_pour_suivre_la_satisfaction_client\mission\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Desktop\Openclassrooms2026\P5_Manipulez_une_base_de_données_avec_SQL_pour_suivre_la_satisfaction_client\livrables\projet-ligue1\mission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDCFA85-3CA3-4F99-B7CA-4440B6EF7A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5ED78E-B875-415A-9D63-BDEC6257E079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="420" windowWidth="21600" windowHeight="13815" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="joueurs" sheetId="1" r:id="rId1"/>
+    <sheet name="joueur" sheetId="1" r:id="rId1"/>
     <sheet name="temps_de_jeu" sheetId="2" r:id="rId2"/>
     <sheet name="performance" sheetId="3" r:id="rId3"/>
     <sheet name="attendu" sheetId="4" r:id="rId4"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="103">
   <si>
     <t>DICTIONNAIRE DES DONNÉES</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Élémentaire</t>
   </si>
   <si>
-    <t>Clé primaire</t>
-  </si>
-  <si>
     <t>nom_equipe</t>
   </si>
   <si>
@@ -178,9 +175,6 @@
     <t>progression_course</t>
   </si>
   <si>
-    <t>id_source</t>
-  </si>
-  <si>
     <t>age</t>
   </si>
   <si>
@@ -188,12 +182,6 @@
   </si>
   <si>
     <t>note_source</t>
-  </si>
-  <si>
-    <t>Identifiant source</t>
-  </si>
-  <si>
-    <t>Nom du joueur</t>
   </si>
   <si>
     <t>Âge du joueur</t>
@@ -206,9 +194,6 @@
   </si>
   <si>
     <t>Text</t>
-  </si>
-  <si>
-    <t>≥ 15</t>
   </si>
   <si>
     <t>buts</t>
@@ -322,21 +307,58 @@
     <t>Clé primaire ; utilisé comme référence dans joueur</t>
   </si>
   <si>
-    <t>Donnée issue d’une source externe</t>
+    <t>id_joueur_source</t>
   </si>
   <si>
-    <t>Valeur estimée, non contractuelle</t>
+    <t>Identifiant du joueur dans la source salaire</t>
+  </si>
+  <si>
+    <t>Nom du joueur dans la source salaire</t>
+  </si>
+  <si>
+    <t>Identifiant joueur rattaché à la table joueur</t>
+  </si>
+  <si>
+    <t>Clé primaire de la table salaire_source. Identifiant conservé pour assurer la traçabilité de la donnée source.</t>
+  </si>
+  <si>
+    <t>Donnée issue d’une source externe. Champ obligatoire.</t>
+  </si>
+  <si>
+    <t>Valeur positive ou nulle. Peut être utilisée pour aider au rapprochement avec la table joueur.</t>
+  </si>
+  <si>
+    <t>Valeur estimée, non contractuelle. Doit être positive ou nulle.</t>
+  </si>
+  <si>
+    <t>Peut être nul. Permet d’indiquer la fiabilité ou l’origine de l’estimation.</t>
+  </si>
+  <si>
+    <t>Non calculé</t>
+  </si>
+  <si>
+    <t>Clé étrangère optionnelle vers joueur(id_joueur). Renseignée uniquement si la correspondance avec la table joueur est fiable. Peut être nul si aucun rattachement n’est possible.</t>
+  </si>
+  <si>
+    <t>Repris depuis id_joueur_source uniquement si l’identifiant existe dans la table joueur</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -373,6 +395,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -394,56 +429,327 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="54">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -639,44 +945,44 @@
   </dxfs>
   <tableStyles count="8">
     <tableStyle name="Joueurs-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="firstRowStripe" dxfId="22"/>
-      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="53"/>
+      <tableStyleElement type="firstRowStripe" dxfId="52"/>
+      <tableStyleElement type="secondRowStripe" dxfId="51"/>
     </tableStyle>
     <tableStyle name="Temps de jeu-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="secondRowStripe" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="50"/>
+      <tableStyleElement type="firstRowStripe" dxfId="49"/>
+      <tableStyleElement type="secondRowStripe" dxfId="48"/>
     </tableStyle>
     <tableStyle name="Performance-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="47"/>
+      <tableStyleElement type="firstRowStripe" dxfId="46"/>
+      <tableStyleElement type="secondRowStripe" dxfId="45"/>
     </tableStyle>
     <tableStyle name="Attendu-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="firstRowStripe" dxfId="13"/>
-      <tableStyleElement type="secondRowStripe" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="44"/>
+      <tableStyleElement type="firstRowStripe" dxfId="43"/>
+      <tableStyleElement type="secondRowStripe" dxfId="42"/>
     </tableStyle>
     <tableStyle name="Progression-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="41"/>
+      <tableStyleElement type="firstRowStripe" dxfId="40"/>
+      <tableStyleElement type="secondRowStripe" dxfId="39"/>
     </tableStyle>
     <tableStyle name="Position-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="firstRowStripe" dxfId="37"/>
+      <tableStyleElement type="secondRowStripe" dxfId="36"/>
     </tableStyle>
     <tableStyle name="Equipe-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="35"/>
+      <tableStyleElement type="firstRowStripe" dxfId="34"/>
+      <tableStyleElement type="secondRowStripe" dxfId="33"/>
     </tableStyle>
     <tableStyle name="Salaire-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="32"/>
+      <tableStyleElement type="firstRowStripe" dxfId="31"/>
+      <tableStyleElement type="secondRowStripe" dxfId="30"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -701,37 +1007,37 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RÈGLE DE GESTION"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="RÈGLE DE CALCUL"/>
   </tableColumns>
-  <tableStyleInfo name="Joueurs-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A5:G10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A5:G10" dataDxfId="29">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CODE"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="SIGNIFICATION"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="TYPE"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="LONGUEUR"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="NATURE"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="RÈGLE DE GESTION"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="RÈGLE DE CALCUL"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CODE" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="SIGNIFICATION" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="TYPE" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="LONGUEUR" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="NATURE" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="RÈGLE DE GESTION" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="RÈGLE DE CALCUL" dataDxfId="22"/>
   </tableColumns>
-  <tableStyleInfo name="Temps de jeu-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="A5:G13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="A5:G13" dataDxfId="21">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="CODE"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SIGNIFICATION"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="TYPE"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="LONGUEUR"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="NATURE"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="RÈGLE DE GESTION"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="RÈGLE DE CALCUL"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="CODE" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SIGNIFICATION" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="TYPE" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="LONGUEUR" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="NATURE" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="RÈGLE DE GESTION" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="RÈGLE DE CALCUL" dataDxfId="14"/>
   </tableColumns>
-  <tableStyleInfo name="Performance-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -746,7 +1052,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="RÈGLE DE GESTION"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="RÈGLE DE CALCUL"/>
   </tableColumns>
-  <tableStyleInfo name="Attendu-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -761,7 +1067,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="RÈGLE DE GESTION"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="RÈGLE DE CALCUL"/>
   </tableColumns>
-  <tableStyleInfo name="Progression-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -776,37 +1082,37 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="RÈGLE DE GESTION"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="RÈGLE DE CALCUL"/>
   </tableColumns>
-  <tableStyleInfo name="Position-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table_7" displayName="Table_7" ref="A5:G7">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="CODE"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="SIGNIFICATION"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="TYPE"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LONGUEUR"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="NATURE"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="RÈGLE DE GESTION"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="CODE" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="SIGNIFICATION" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="TYPE" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LONGUEUR" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="NATURE" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="RÈGLE DE GESTION" dataDxfId="8"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="RÈGLE DE CALCUL"/>
   </tableColumns>
-  <tableStyleInfo name="Equipe-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table_8" displayName="Table_8" ref="A5:G10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table_8" displayName="Table_8" ref="A5:G11" dataDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="CODE"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="SIGNIFICATION"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="TYPE"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="LONGUEUR"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="NATURE"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="RÈGLE DE GESTION"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="RÈGLE DE CALCUL"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="CODE" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="SIGNIFICATION" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="TYPE" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="LONGUEUR" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="NATURE" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="RÈGLE DE GESTION" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="RÈGLE DE CALCUL" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="Salaire-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1012,24 +1318,24 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" customWidth="1"/>
     <col min="6" max="6" width="48.42578125" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1121,8 +1427,8 @@
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>71</v>
+      <c r="B9" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>8</v>
@@ -1133,8 +1439,8 @@
       <c r="E9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>73</v>
+      <c r="F9" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="G9" s="6"/>
     </row>
@@ -1154,17 +1460,17 @@
       <c r="E10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>74</v>
+      <c r="F10" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>72</v>
+      <c r="B11" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>8</v>
@@ -1175,8 +1481,8 @@
       <c r="E11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>75</v>
+      <c r="F11" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="G11" s="6"/>
     </row>
@@ -1207,7 +1513,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -2347,25 +2653,25 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="62.140625" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" customWidth="1"/>
     <col min="7" max="7" width="34.42578125" customWidth="1"/>
     <col min="8" max="25" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -2390,111 +2696,111 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="26"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="26"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="D10" s="26">
+        <v>6.2</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="26" t="s">
         <v>77</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="9">
-        <v>6.2</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3672,24 +3978,24 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
+    <col min="2" max="2" width="41.5703125" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="17" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -3707,180 +4013,180 @@
       <c r="E5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="C11" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B13" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E13" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="6"/>
+      <c r="F13" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
@@ -3888,7 +4194,7 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="F14" s="16"/>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3897,7 +4203,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3906,7 +4212,7 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="F16" s="16"/>
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3915,7 +4221,7 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3924,7 +4230,7 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="F18" s="16"/>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3933,7 +4239,7 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="F19" s="16"/>
       <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3942,7 +4248,7 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
+      <c r="F20" s="16"/>
       <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3951,7 +4257,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="16"/>
       <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3960,7 +4266,7 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="F22" s="16"/>
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3969,7 +4275,7 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
+      <c r="F23" s="16"/>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3978,7 +4284,7 @@
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="F24" s="16"/>
       <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3987,7 +4293,7 @@
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="16"/>
       <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3996,7 +4302,7 @@
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="F26" s="16"/>
       <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4005,7 +4311,7 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
+      <c r="F27" s="16"/>
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4014,7 +4320,7 @@
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="F28" s="16"/>
       <c r="G28" s="6"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4023,7 +4329,7 @@
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
+      <c r="F29" s="16"/>
       <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4032,7 +4338,7 @@
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+      <c r="F30" s="16"/>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5022,24 +5328,24 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -5065,11 +5371,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>36</v>
+      <c r="B6" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>8</v>
@@ -5077,74 +5383,74 @@
       <c r="D6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>80</v>
+      <c r="F6" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>88</v>
+        <v>39</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="9">
         <v>6.2</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>39</v>
+      <c r="F7" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="G7" s="6"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>44</v>
       </c>
       <c r="D8" s="9">
         <v>6.2</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>39</v>
+      <c r="F8" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="G8" s="6"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="9">
         <v>6.2</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>39</v>
+      <c r="F9" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="G9" s="6"/>
     </row>
@@ -6310,7 +6616,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="1">
@@ -6334,15 +6640,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -6368,11 +6674,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>36</v>
+      <c r="B6" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>8</v>
@@ -6383,17 +6689,17 @@
       <c r="E6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>80</v>
+      <c r="F6" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>90</v>
+      <c r="A7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>8</v>
@@ -6404,17 +6710,17 @@
       <c r="E7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>39</v>
+      <c r="F7" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>91</v>
+      <c r="A8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>86</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>8</v>
@@ -6425,17 +6731,17 @@
       <c r="E8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>39</v>
+      <c r="F8" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>92</v>
+      <c r="A9" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>8</v>
@@ -6446,8 +6752,8 @@
       <c r="E9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>39</v>
+      <c r="F9" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="G9" s="11"/>
     </row>
@@ -7640,20 +7946,20 @@
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+    <col min="6" max="6" width="46.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -7682,10 +7988,10 @@
       <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="4">
@@ -7694,17 +8000,17 @@
       <c r="E6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>95</v>
+      <c r="F6" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>94</v>
+        <v>30</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>12</v>
@@ -8927,20 +9233,20 @@
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+    <col min="6" max="6" width="47.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -8981,17 +9287,17 @@
       <c r="E6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>95</v>
+      <c r="F6" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>12</v>
@@ -9003,7 +9309,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" s="6"/>
     </row>
@@ -10210,27 +10516,27 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+    <col min="6" max="6" width="49.5703125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="40.42578125" style="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -10239,132 +10545,156 @@
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="19">
+        <v>100</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B9" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="19">
+        <v>12.2</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C10" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D11" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E11" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="5">
-        <v>100</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="5">
-        <v>12.2</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="F11" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
@@ -10372,8 +10702,8 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
@@ -10381,8 +10711,8 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
@@ -10390,8 +10720,8 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
@@ -10399,8 +10729,8 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
@@ -10408,8 +10738,8 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
@@ -10417,8 +10747,8 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
@@ -10426,8 +10756,8 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
@@ -10435,8 +10765,8 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
@@ -10444,8 +10774,8 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
@@ -10453,8 +10783,8 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
@@ -10462,8 +10792,8 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
@@ -10471,8 +10801,8 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
@@ -10480,8 +10810,8 @@
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
@@ -10489,8 +10819,8 @@
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
@@ -10498,8 +10828,8 @@
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
@@ -10507,8 +10837,8 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
@@ -10516,8 +10846,8 @@
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
@@ -10525,8 +10855,8 @@
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
@@ -10534,8 +10864,8 @@
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
@@ -10543,8 +10873,8 @@
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
